--- a/2022 data/excel_outputs/361_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/361_boothwise_data.xlsx
@@ -14,798 +14,1146 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="405">
   <si>
     <t>AC 361 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0##0 ######## ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>###### ### ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ;##0#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ;#0#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##0 2 ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ;#########ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;####ddh ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;####ddh ;#0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0######### ##0 #########e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0######### ##0 #########e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0######### ##0 #########e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0######### ##0 #########e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ####.2 ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ####.6;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.6;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.7;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.8;#0ddh</t>
-  </si>
-  <si>
-    <t>########## ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #####e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #####e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #####e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #####e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #####e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #####e ####.6;#0ddh</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #####e ####.7;#0ddh</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #####e ####.8;#0ddh</t>
-  </si>
-  <si>
-    <t>######### ##### ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0#0##0 ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0#0##0 ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ####.1;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>##### ##### #.###### ######e ####.1</t>
-  </si>
-  <si>
-    <t>##### ##### #.###### ######e ####.2</t>
-  </si>
-  <si>
-    <t>##### ##### #.###### ######e ####.3</t>
-  </si>
-  <si>
-    <t>##### ##### #.###### ######e ####.4</t>
-  </si>
-  <si>
-    <t>##### ##### #.###### ######e ####.5</t>
-  </si>
-  <si>
-    <t>##### ##### #.###### ######e ####.6</t>
-  </si>
-  <si>
-    <t>##### ##### #.###### ######e ####.7</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ########e ####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ########e ####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ########e ####.3</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>##### ####### #### ###### ########e #####e ####.1</t>
-  </si>
-  <si>
-    <t>##### ####### #### ###### ########e #####e ####.2</t>
-  </si>
-  <si>
-    <t>##### ####### #### ###### ########e #####e ####.3</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.1</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.2</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.3</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.4</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.5</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.6</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.7</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.8</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.9</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.10</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #####e ####.11</t>
-  </si>
-  <si>
-    <t>#### ### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>#### ### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ####0##0 #### ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ####0##0 ####### ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ####0##0 #######e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ####0##0 #######e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ####0##0 #######e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ####0##0 #######e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0#### #### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0#### #### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##### #### #0##0##0 ##### #####e ####.1</t>
-  </si>
-  <si>
-    <t>##### #### #0##0##0 ##### #####e ####.2</t>
-  </si>
-  <si>
-    <t>##### #### #0##0##0 ##### #####e ####.3</t>
-  </si>
-  <si>
-    <t>##### #### #0##0##0 ##### #####e ####.4</t>
-  </si>
-  <si>
-    <t>##### ####### #####e #####e ####.1</t>
-  </si>
-  <si>
-    <t>##### ####### #####e #####e ####.2</t>
-  </si>
-  <si>
-    <t>##### ####### #####e #####e ####.3</t>
-  </si>
-  <si>
-    <t>##### ####### #####e #####e ####.4</t>
-  </si>
-  <si>
-    <t>##### ####### #####e #####e ####.5</t>
-  </si>
-  <si>
-    <t>##### ####### #####e #####e ####.6</t>
-  </si>
-  <si>
-    <t>##### #0####0##0 ;###### ##### #####ddhe ####.1</t>
-  </si>
-  <si>
-    <t>##### #0####0##0 ;###### ##### #####ddhe ####.2</t>
-  </si>
-  <si>
-    <t>##0##0#0 ######## ### ;###### ##### #####ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ;###### ##### #####ddhe ####.1</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ;###### ##### #####ddhe ####.2</t>
-  </si>
-  <si>
-    <t>##0##0#0 ######## ;###### ##### #####ddhe ####.1</t>
-  </si>
-  <si>
-    <t>##0##0#0 ######## ;###### ##### #####ddhe ####.2</t>
-  </si>
-  <si>
-    <t>####### ### ##0#0 #### #### ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####### ### ##0#0 #### #### ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####### ####### ##### ##### #####e ####.1;#0ddh</t>
-  </si>
-  <si>
-    <t>####### ####### ##### ##### #####e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>####### ####### ##### ##### #####e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>####### ####### ##### ##### #####e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>####### ####### ##### ##### #####e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>####### ####### ##### ##### #####e ####.6;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ###### #####e #####e ####.1;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ###### #####e #####e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ###### #####e #####e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ###### #####e #####e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ###### #####e #####e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ###### #####e #####e ####.6;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.6;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.7;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.8;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.9;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #########e ####.10;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;#0#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##0.2 ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##0.2 ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0######</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ### ###</t>
-  </si>
-  <si>
-    <t>###### ### ########</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>##0##0 ##### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ###### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #########</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #####</t>
-  </si>
-  <si>
-    <t>##0##0 ##### #### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### #### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0###### ##0 ###</t>
-  </si>
-  <si>
-    <t>##0#0##0##0###### ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0#0##0##0###### ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### ## #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ## #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####e ####.1;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####e ####.5;#0ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #########e ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 #########e ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ########e ####.3</t>
-  </si>
-  <si>
-    <t>####0##0 #######e ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 #######e ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ### #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### #### ### #####e ####.1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### #### ### #####e ####.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### #### ### #####e ####.3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### #### ### #####e ####.4</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ### #####e##### ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ### #####e##### ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ### #####e##### ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ### #####e##### ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### #####</t>
-  </si>
-  <si>
-    <t>#0#0##0#0##0 ####e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>#0#0##0#0##0 ####e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>#0#0##0#0##0 ####e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>#0#0##0#0##0 ####e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>### ####### ##### ##### #####e ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>### ####### ##### ##### #####e ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>#### #### ######## ###### #####e #####e ####.1</t>
-  </si>
-  <si>
-    <t>#### #### ######## ###### #####e #####e ####.2</t>
-  </si>
-  <si>
-    <t>#### #### ######## ###### #####e #####e ####.3</t>
-  </si>
-  <si>
-    <t>#### #### ######## ###### #####e #####e ####.4</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ###### ##### #### #### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ###### ##### #### #### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ##0 #### ###### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ###### ;########ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 #### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0###### #### ##0 #### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 #### #### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ######## #### ####### ## ####e ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ######## #### ####### ## ####e ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;######## ####ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0######## ##### #####.######</t>
-  </si>
-  <si>
-    <t>####0##0###### ######## ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0###### ######## ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0 ####e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0 ####e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0 ####e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>#0##0##0 ####e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 1 ##### #####. #########e ####.1;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 1 ##### #####. #########e ####.2;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 1 ##### #####. #########e ####.3;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 1 ##### #####. #########e ####.4;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 2 ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 2 ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.8;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####.9;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0 ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0 ##### ;#0ddh</t>
+    <t>P.P.DHARMPURA</t>
+  </si>
+  <si>
+    <t>P.P.KUMHAILA</t>
+  </si>
+  <si>
+    <t>P.P.DHARHARA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.DHARHARA,SOUTH</t>
+  </si>
+  <si>
+    <t>JR.H.S.DHARHARA</t>
+  </si>
+  <si>
+    <t>P.P.BHARATPURA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.BHARATPURA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P BRAHMAIN, NORTH</t>
+  </si>
+  <si>
+    <t>P.P BRAHMAIN , NORTH</t>
+  </si>
+  <si>
+    <t>P.P.BRAHMAIN KA DERA</t>
+  </si>
+  <si>
+    <t>P.P.PIPARAULI</t>
+  </si>
+  <si>
+    <t>P.P.BASANTPUR</t>
+  </si>
+  <si>
+    <t>P.P.BASANTPUR,NO-1</t>
+  </si>
+  <si>
+    <t>MIDDLE P.P.BASANTPUR NO.1</t>
+  </si>
+  <si>
+    <t>P.P.BASANTPUR NO.2,</t>
+  </si>
+  <si>
+    <t>NORTH P.P.BASANTPUR NO.2,</t>
+  </si>
+  <si>
+    <t>SOUTH P.P.HANUMANGANJ</t>
+  </si>
+  <si>
+    <t>P.P.HANUMANGANJ</t>
+  </si>
+  <si>
+    <t>P.P.JIRABASTI</t>
+  </si>
+  <si>
+    <t>JR.H.S.JIRABASTI,NORTH</t>
+  </si>
+  <si>
+    <t>JR.H.S.JIRABASTI,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P PATAKHAULI (NAGARI)</t>
+  </si>
+  <si>
+    <t>P.P.DEOKALI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.DEOKALI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.BAHADUR</t>
+  </si>
+  <si>
+    <t>MU.BRAHMAIN,EAST P.P.BAHADUR</t>
+  </si>
+  <si>
+    <t>MU.BRAHMAIN,WEST P.P.BAHADUR</t>
+  </si>
+  <si>
+    <t>MU.BRAHMAIN,MIDDLE P.P.PARIKHARA</t>
+  </si>
+  <si>
+    <t>P.P.PARIKHARA</t>
+  </si>
+  <si>
+    <t>POLITEKNIC</t>
+  </si>
+  <si>
+    <t>SCHOOL,BALLIA POLITEKNIC</t>
+  </si>
+  <si>
+    <t>SCHOOL,BALLIA P.P.TIKHAMPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.TIKHAMPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.TIKHAMPUR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.HARPUR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.HARPUR,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.HARPUR,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.HARPUR,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.HARPUR,WEST</t>
+  </si>
+  <si>
+    <t>JR.H.S.HARPUR,MIDDLE</t>
+  </si>
+  <si>
+    <t>MUNICIPAL BOARD,NORTH</t>
+  </si>
+  <si>
+    <t>MUNICIPAL BOARD,SOUTH</t>
+  </si>
+  <si>
+    <t>TOWN DEGREE</t>
+  </si>
+  <si>
+    <t>COLLEG,BALLIA,NORTH TOWN INTER</t>
+  </si>
+  <si>
+    <t>COLLEG,BALLIA,MIDDLE TOWN INTER</t>
+  </si>
+  <si>
+    <t>COLLEG,BALLIA,MIDDLE KUNWAR SINGH I.C.BALLIA</t>
+  </si>
+  <si>
+    <t>KUNWAR SINGH I.C.BALLIA</t>
+  </si>
+  <si>
+    <t>ISLAMIA SCHOOL</t>
+  </si>
+  <si>
+    <t>PARMANDAPUR,NORTH P.P.PARMANDAPUR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.PARMANDAPUR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.AMADARI</t>
+  </si>
+  <si>
+    <t>P.P.A.M.,HAIDARCHAK</t>
+  </si>
+  <si>
+    <t>P.P.PANDEYPUR</t>
+  </si>
+  <si>
+    <t>MISHRA,NORTH P.P.NIDHIRIA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.NIDHIRIA,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.NIDHIRIA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.NIDHIRIA,SOUTH</t>
+  </si>
+  <si>
+    <t>FAROGE TAMIL A-NISVA</t>
+  </si>
+  <si>
+    <t>UMARGANG FAROGE TAMIL A-NISVA</t>
+  </si>
+  <si>
+    <t>UMARGANG P.P.DEORIAKALA</t>
+  </si>
+  <si>
+    <t>P.P.MANSOORCHAK</t>
+  </si>
+  <si>
+    <t>P.P.NASIRABAD,EAST</t>
+  </si>
+  <si>
+    <t>P.P.DARAMPUR</t>
+  </si>
+  <si>
+    <t>P.P.MALDEPUR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.MALDEPUR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.HAIBATPUR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.HAIBATPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.KHORIPAKAD</t>
+  </si>
+  <si>
+    <t>P.P.JALALPUR</t>
+  </si>
+  <si>
+    <t>P.P.RAMPUR</t>
+  </si>
+  <si>
+    <t>MAHAWAL,WEST P.P.RAMPUR</t>
+  </si>
+  <si>
+    <t>MAHAWAL,MIDDLE P.P.RAMPUR</t>
+  </si>
+  <si>
+    <t>MAHAWAL,WEST P.P.ISLAMIA</t>
+  </si>
+  <si>
+    <t>SCHOOL,BAHERI P.P.ISLAMIA</t>
+  </si>
+  <si>
+    <t>SCHOOL,BAHERI P.P.BAHERI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.BAHERI,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.BAHERI WEST</t>
+  </si>
+  <si>
+    <t>GOVT.I.C.BALLIA,EAST</t>
+  </si>
+  <si>
+    <t>GOVT.I.C.BALLIA,WEST</t>
+  </si>
+  <si>
+    <t>GOVT.I.C.BALLIA</t>
+  </si>
+  <si>
+    <t>TOWN HAL,BALLIA EAST</t>
+  </si>
+  <si>
+    <t>TOWN HAL,BALLIA WEST</t>
+  </si>
+  <si>
+    <t>P.V. AAJAD VISHUNIPUR</t>
+  </si>
+  <si>
+    <t>P.P.SUBHASH</t>
+  </si>
+  <si>
+    <t>NAGAR,BANKATA,EAST P.P.SUBHASH</t>
+  </si>
+  <si>
+    <t>NAGAR,BANKATA,MIDDLE P.P.SUBHASH</t>
+  </si>
+  <si>
+    <t>NAGAR,BANKATA,MIDDLE P.P.VIJAIPUR</t>
+  </si>
+  <si>
+    <t>P.P.VIJAIPUR</t>
+  </si>
+  <si>
+    <t>U.M.V.JATAHA</t>
+  </si>
+  <si>
+    <t>BABA,BALLIA,WEST U.M.V.JATAHA</t>
+  </si>
+  <si>
+    <t>P.P.VAJIRAPUR</t>
+  </si>
+  <si>
+    <t>GULAB DEVI KANYA</t>
+  </si>
+  <si>
+    <t>H.S.SCHOOL,BALLIA GULAB DEVI KANYA</t>
+  </si>
+  <si>
+    <t>H.S.SCHOOL,BALLIA JUBALI SANSKRIT</t>
+  </si>
+  <si>
+    <t>COLLEGE JUBALI SANSKRIT</t>
+  </si>
+  <si>
+    <t>COLLEGE AADARSH U.P.P (TEHSILI</t>
+  </si>
+  <si>
+    <t>SCHOOL PARISAR) AADARSH U.P.P (TEHSILI</t>
+  </si>
+  <si>
+    <t>SCHOOL PARISAR) B.S.A TRENIG HAL (TEHSILI</t>
+  </si>
+  <si>
+    <t>SCHOOL PARISAR) AADARSH P.P (TEHSILI</t>
+  </si>
+  <si>
+    <t>SCHOOL PARISAR) B.S.A KARYALAY (TEHSILI</t>
+  </si>
+  <si>
+    <t>SCHOOL PARISAR) DAYANAND BAL</t>
+  </si>
+  <si>
+    <t>V.M.ARAY SMAJ DAYANAND BAL</t>
+  </si>
+  <si>
+    <t>V.M.ARAY SMAJ LAKSHAMI RAJ DEVI</t>
+  </si>
+  <si>
+    <t>I.C.BALLIA,NORTH LAKSHAMI RAJ DEVI</t>
+  </si>
+  <si>
+    <t>I.C.BALLIA,MIDDLE LAKSHAMI RAJ DEVI</t>
+  </si>
+  <si>
+    <t>I.C.BALLIA,SOUTH LAKSHAMI RAJ DEVI</t>
+  </si>
+  <si>
+    <t>I.C.BALLIA,SOUTH SATISHCHANDRA</t>
+  </si>
+  <si>
+    <t>COLLEGE,NORTH SATISHCHANDRA</t>
+  </si>
+  <si>
+    <t>COLLEGE,MIDDLE SATISHCHANDRA</t>
+  </si>
+  <si>
+    <t>COLLEGE,MIDDLE P.P.BHRIGU ASHRAM,EAST</t>
+  </si>
+  <si>
+    <t>P.P.BHRIGU ASHRAM,WEST</t>
+  </si>
+  <si>
+    <t>P.P.BHRIGU ASHRAM,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.BHRIGU</t>
+  </si>
+  <si>
+    <t>ASHRAM,EAST JR.H.S.BHRIGU</t>
+  </si>
+  <si>
+    <t>ASHRAM,MIDDLE JR.H.S.BHRIGU</t>
+  </si>
+  <si>
+    <t>ASHRAM,MIDDLE KANYA P.P.BHRIGU</t>
+  </si>
+  <si>
+    <t>ASHRAM KANYA P.P.BHRIGU</t>
+  </si>
+  <si>
+    <t>ASHRAM P.P.KADAMTAR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.KADAMTAR,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.KADAMTAR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.AMRITPALI EAST</t>
+  </si>
+  <si>
+    <t>P.P.AMRITPALI WEST</t>
+  </si>
+  <si>
+    <t>P.P.SUREMANPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SUREMANPUR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.SONADABAR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.SONADABAR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.TAKARSAN,EAST</t>
+  </si>
+  <si>
+    <t>P.P.TAKARSAN,WEST</t>
+  </si>
+  <si>
+    <t>P.P.GOTHAHULI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.GOTHAHULI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.SHANKARPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SHANKARPUR,WEST</t>
+  </si>
+  <si>
+    <t>I.C.MAJHAULI</t>
+  </si>
+  <si>
+    <t>P.P.BAJAHA</t>
+  </si>
+  <si>
+    <t>P.P.SONPURWAKALA</t>
+  </si>
+  <si>
+    <t>TAGHARAULI,EAST</t>
+  </si>
+  <si>
+    <t>TAGHARAULI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.CHHODAHAR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.CHHODAHAR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.NAWANAGAR</t>
+  </si>
+  <si>
+    <t>P.P.GAJIAPUR</t>
+  </si>
+  <si>
+    <t>KANYA P.P.SHRIPUR</t>
+  </si>
+  <si>
+    <t>P.P.BHIKHPUR</t>
+  </si>
+  <si>
+    <t>P.P.PARASPUR</t>
+  </si>
+  <si>
+    <t>JR.H.S.SLEMPUR</t>
+  </si>
+  <si>
+    <t>P.P.DUBAULI</t>
+  </si>
+  <si>
+    <t>P.P.GHAGHARAULI</t>
+  </si>
+  <si>
+    <t>P.P.DUMARI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.DUMARI,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.SARAYA,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SARAYA,WEST</t>
+  </si>
+  <si>
+    <t>P.P.FULWARIA</t>
+  </si>
+  <si>
+    <t>P.V.BABHANAULI NEW</t>
+  </si>
+  <si>
+    <t>BUILDING PANCHAYAT BHAWAN</t>
+  </si>
+  <si>
+    <t>NARAINPUR H.S.SCHOOL AMAGHAT</t>
+  </si>
+  <si>
+    <t>H.S.SCHOOL AMAGHAT</t>
+  </si>
+  <si>
+    <t>P.P.BRAHMDEVATA</t>
+  </si>
+  <si>
+    <t>P.P.SEMARI</t>
+  </si>
+  <si>
+    <t>P.P.DEAULI</t>
+  </si>
+  <si>
+    <t>H.S.SCHOOL,CHHATA,NORT</t>
+  </si>
+  <si>
+    <t>H H.S.SCHOOL,CHHATA,SOUT</t>
+  </si>
+  <si>
+    <t>H P.P.CHHATA,OLD BHAWAN</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR</t>
+  </si>
+  <si>
+    <t>P.P.RUSTAMPUR</t>
+  </si>
+  <si>
+    <t>P.P.KUNWAR JASHAON</t>
+  </si>
+  <si>
+    <t>P.P.BAGHAULI</t>
+  </si>
+  <si>
+    <t>P.P.MADHOPUR</t>
+  </si>
+  <si>
+    <t>P.P.PRATAPPUR</t>
+  </si>
+  <si>
+    <t>P.P.MANIYARI JASHAON</t>
+  </si>
+  <si>
+    <t>P.P.UDHODAWANI</t>
+  </si>
+  <si>
+    <t>JR.H.S.SHITAL</t>
+  </si>
+  <si>
+    <t>DAWANI,EAST JR.H.S.SHITAL</t>
+  </si>
+  <si>
+    <t>DAWANI,WEST P.P.CHANDRAPURA</t>
+  </si>
+  <si>
+    <t>P.P.TIWARI BARAHATA</t>
+  </si>
+  <si>
+    <t>P.P.BHUILI</t>
+  </si>
+  <si>
+    <t>P.P.SARANK</t>
+  </si>
+  <si>
+    <t>P.P.BALIPUR</t>
+  </si>
+  <si>
+    <t>P.P.MISHRAULI</t>
+  </si>
+  <si>
+    <t>P.P.SHER,WEST</t>
+  </si>
+  <si>
+    <t>P.P.SHER,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.SHER,EAST</t>
+  </si>
+  <si>
+    <t>P.P.PATHAKAULI TA. SHER</t>
+  </si>
+  <si>
+    <t>P.P.SOHILPUR</t>
+  </si>
+  <si>
+    <t>P.P.CHANDWAK</t>
+  </si>
+  <si>
+    <t>P.P.PURAS,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.PURAS,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.ROHUWA,EAST</t>
+  </si>
+  <si>
+    <t>P.P.ROHUWA,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.ROHUWA,WEST</t>
+  </si>
+  <si>
+    <t>P.P.BASUNDHARPAH</t>
+  </si>
+  <si>
+    <t>P.P.PINDARI</t>
+  </si>
+  <si>
+    <t>GOVT.KANYA B.V.RAMPUR</t>
+  </si>
+  <si>
+    <t>TITIHI,EAST GOVT.KANYA B.V.RAMPUR</t>
+  </si>
+  <si>
+    <t>TITIHI,WEST GOVT.KANYA B.V.RAMPUR</t>
+  </si>
+  <si>
+    <t>TITIHI,WEST P.P.CHHAPARA</t>
+  </si>
+  <si>
+    <t>P.P.CHHAPARA</t>
+  </si>
+  <si>
+    <t>P.P.DADA KE</t>
+  </si>
+  <si>
+    <t>CHHAPARA,EAST P.P.DADA KE</t>
+  </si>
+  <si>
+    <t>CHHAPARA,WEST JR.H.S.AKHAR,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.AKHAR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.AKHAR</t>
+  </si>
+  <si>
+    <t>P.P.PIPARA</t>
+  </si>
+  <si>
+    <t>P.P.SAWARUBANDH,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SAWARUBANDH,WEST</t>
+  </si>
+  <si>
+    <t>P.P.UDAYPURA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.UDAYPURA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.JAMUA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.JAMUA,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.JAMUA,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.JAMUA</t>
+  </si>
+  <si>
+    <t>P.P.SAHARASPALI</t>
+  </si>
+  <si>
+    <t>P.P.BANDHUCHAK</t>
+  </si>
+  <si>
+    <t>P.P.PANDEYPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.PANDEYPUR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.MOHAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA,NORTH P.P.MOHAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA,SOUTH P.P.MOHAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA,SOUTH P.P.GHODAHARA,EAST</t>
+  </si>
+  <si>
+    <t>P.P.GHODAHARA,WEST</t>
+  </si>
+  <si>
+    <t>JR.H.S.GHODAHARA,NORTH</t>
+  </si>
+  <si>
+    <t>JR.H.S.GHODAHARA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.SHIVPUR DIYAR NEW</t>
+  </si>
+  <si>
+    <t>BASTI,EAST KANYA P.P.SHIVPUR DIYAR</t>
+  </si>
+  <si>
+    <t>NEW BASTI,WEST KANYA P.P.SHIVPUR DIYAR</t>
+  </si>
+  <si>
+    <t>NEW BASTI,MIDDLE KANYA P.P.SHIVPUR DIYAR</t>
+  </si>
+  <si>
+    <t>NEW BASTI KANYA P.P.SHIVPUR DIYAR</t>
+  </si>
+  <si>
+    <t>NEW BASTI P.P.SHIVPUR DIYAR NEW</t>
+  </si>
+  <si>
+    <t>BASTI JANARI,WEST P.P.SHIVPUR DIYAR NEW</t>
+  </si>
+  <si>
+    <t>BASTI JANARI,MIDDLE P.P.SHIVPUR DIYAR NEW</t>
+  </si>
+  <si>
+    <t>BASTI JANARI,MIDDLE P.P.MAFI DUBAHAD</t>
+  </si>
+  <si>
+    <t>S.M.P.I.C NAGWA,WEST</t>
+  </si>
+  <si>
+    <t>S.M.P.I.C NAGWA,EAST</t>
+  </si>
+  <si>
+    <t>P.P. NAGWA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P. NAGWA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.JANARI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.JANARI,WEST</t>
+  </si>
+  <si>
+    <t>KANYA P.P.JANADI,EAST</t>
+  </si>
+  <si>
+    <t>KANYA P.P.JANADI,WEST</t>
+  </si>
+  <si>
+    <t>R.S.K.I C..DUBAHAD,WEST-</t>
+  </si>
+  <si>
+    <t>SOUTH R.S.K.I C..DUBAHAD,EAST-</t>
+  </si>
+  <si>
+    <t>SOUTH R.S.K.I C..DUBAHAD WEST-</t>
+  </si>
+  <si>
+    <t>SOUTH K.D.B DEGREE COLLEGE</t>
+  </si>
+  <si>
+    <t>DUBAHADWEST K.D.B DEGREE COLLEGE</t>
+  </si>
+  <si>
+    <t>DUBAHAD,MIDDLE K.D.B DEGREE COLLEGE</t>
+  </si>
+  <si>
+    <t>DUBAHAD ,EAST P.P.DUBAHAD,EAST</t>
+  </si>
+  <si>
+    <t>P.P.DUBAHAD,WEST</t>
+  </si>
+  <si>
+    <t>JR.H.S.SHIVPUR DIYAR</t>
+  </si>
+  <si>
+    <t>NUMBARI DERA KESHAV JR.H.S.SHIVPUR DIYAR</t>
+  </si>
+  <si>
+    <t>NUMBARI DERA KESHAV P.P.SHIVPUR DIYAR NO.</t>
+  </si>
+  <si>
+    <t>DERA RAMDHANI P.P.SHIVPUR DIYAR NO.</t>
+  </si>
+  <si>
+    <t>DERA RAMDHANI P.P.SHIVPUR DIYAR</t>
+  </si>
+  <si>
+    <t>SOMALI(PRANPUR) P.P.SHIVPUR DIYAR NO.</t>
+  </si>
+  <si>
+    <t>DERA KRIPA RAI,NORTH P.P.SHIVPUR DIYAR NO.</t>
+  </si>
+  <si>
+    <t>DERA KRIPA RAI,SOUTH P.P.SHIVPUR DIYAR NO.</t>
+  </si>
+  <si>
+    <t>DERA DEVI RAI P.P.OJHAWALIA,EAST</t>
+  </si>
+  <si>
+    <t>P.P.OJHAWALIA,WEST</t>
+  </si>
+  <si>
+    <t>JR.H.S.BASARIKPAH,NORTH</t>
+  </si>
+  <si>
+    <t>JR.H.S.BASARIKPAH,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.BASARIKPAH,EAST</t>
+  </si>
+  <si>
+    <t>P.P.BASARIKPAH,WEST</t>
+  </si>
+  <si>
+    <t>KANYA H.S.SNATH</t>
+  </si>
+  <si>
+    <t>PANDEY KE KANYA H.S.SNATH</t>
+  </si>
+  <si>
+    <t>P.P.DOPAHI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.DOPAHI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.NIROOPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.NIROOPUR,WEST</t>
+  </si>
+  <si>
+    <t>U.M.V.NIROOPUR,NORTH</t>
+  </si>
+  <si>
+    <t>U.M.V.NIROOPUR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.REPURA</t>
+  </si>
+  <si>
+    <t>P.P.REPURA, ADDITIONAL</t>
+  </si>
+  <si>
+    <t>ROOM P.P.REPURA,WEST</t>
+  </si>
+  <si>
+    <t>KANYA P.P.REPURA</t>
+  </si>
+  <si>
+    <t>P.P.HARIHARPUR GRAM-</t>
+  </si>
+  <si>
+    <t>REPURA P.P.RAJPUR BADAKIBARI</t>
+  </si>
+  <si>
+    <t>AKAUNA P.P.UDAWAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA,EAST P.P.UDAWAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA,WEST U.M.V.JAWAHI,EAST</t>
+  </si>
+  <si>
+    <t>U.M.V.JAWAHI,MIDDLE</t>
+  </si>
+  <si>
+    <t>U.M.V.JAWAHI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.BAJARAHA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.BAJARAHA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.PARSIYA NO.1, EAST</t>
+  </si>
+  <si>
+    <t>GRAM-SINGHAKUND P.P.PARSIYA NO.1, EAST</t>
+  </si>
+  <si>
+    <t>GRAM-SINGHAKUND P.P.PARSIYA NO.2,EAST</t>
+  </si>
+  <si>
+    <t>P.P.PARSIYA NO.2,WEST</t>
+  </si>
+  <si>
+    <t>P.P.SULTANPUR</t>
+  </si>
+  <si>
+    <t>P.P.BHARSAUTA,EAST</t>
+  </si>
+  <si>
+    <t>P.P.BHARSAUTA,WEST</t>
+  </si>
+  <si>
+    <t>P.P.NANDPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.NANDPUR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.HALDI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.HALDI,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.HALDI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.HALDI,SOUTH-EAST</t>
+  </si>
+  <si>
+    <t>KANYA P.P.HALDI,EAST</t>
+  </si>
+  <si>
+    <t>KANYA P.P.HALDI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.HALDI,NO.2</t>
+  </si>
+  <si>
+    <t>P.P.NEMCHHAPARA MU.</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU.</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>HALDI P.P.NEMCHHAPARA MU. ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -887,8 +1235,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -904,7 +1260,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -912,12 +1268,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1216,91 +1590,169 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>264</v>
+        <v>380</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>381</v>
       </c>
       <c r="E2" t="s">
-        <v>266</v>
+        <v>382</v>
       </c>
       <c r="F2" t="s">
-        <v>267</v>
+        <v>383</v>
       </c>
       <c r="G2" t="s">
-        <v>268</v>
+        <v>384</v>
       </c>
       <c r="H2" t="s">
-        <v>269</v>
+        <v>385</v>
       </c>
       <c r="I2" t="s">
-        <v>270</v>
+        <v>386</v>
       </c>
       <c r="J2" t="s">
-        <v>271</v>
+        <v>387</v>
       </c>
       <c r="K2" t="s">
-        <v>272</v>
+        <v>388</v>
       </c>
       <c r="L2" t="s">
-        <v>273</v>
+        <v>389</v>
       </c>
       <c r="M2" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="N2" t="s">
-        <v>275</v>
+        <v>391</v>
       </c>
       <c r="O2" t="s">
-        <v>276</v>
+        <v>392</v>
       </c>
       <c r="P2" t="s">
-        <v>277</v>
+        <v>393</v>
       </c>
       <c r="Q2" t="s">
-        <v>278</v>
+        <v>394</v>
       </c>
       <c r="R2" t="s">
-        <v>279</v>
+        <v>395</v>
       </c>
       <c r="S2" t="s">
-        <v>280</v>
+        <v>396</v>
       </c>
       <c r="T2" t="s">
-        <v>281</v>
+        <v>397</v>
       </c>
       <c r="U2" t="s">
-        <v>282</v>
+        <v>398</v>
       </c>
       <c r="V2" t="s">
-        <v>283</v>
+        <v>399</v>
       </c>
       <c r="W2" t="s">
-        <v>284</v>
+        <v>400</v>
       </c>
       <c r="X2" t="s">
-        <v>285</v>
+        <v>401</v>
       </c>
       <c r="Y2" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="Z2" t="s">
-        <v>287</v>
+        <v>403</v>
       </c>
       <c r="AA2" t="s">
-        <v>288</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1308,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>814</v>
@@ -1391,7 +1843,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>718</v>
@@ -1474,7 +1926,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>610</v>
@@ -1557,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>1141</v>
@@ -1640,7 +2092,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>872</v>
@@ -1723,7 +2175,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>609</v>
@@ -1806,7 +2258,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>925</v>
@@ -1889,7 +2341,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>661</v>
@@ -1972,7 +2424,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>990</v>
@@ -2055,7 +2507,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>954</v>
@@ -2138,7 +2590,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>630</v>
@@ -2221,7 +2673,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C14">
         <v>1146</v>
@@ -2304,7 +2756,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>989</v>
@@ -2387,7 +2839,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>1123</v>
@@ -2470,7 +2922,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>1018</v>
@@ -2553,7 +3005,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>956</v>
@@ -2636,7 +3088,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>941</v>
@@ -2719,7 +3171,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C20">
         <v>1115</v>
@@ -2802,7 +3254,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>655</v>
@@ -2885,7 +3337,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <v>563</v>
@@ -2968,7 +3420,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>870</v>
@@ -3051,7 +3503,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>680</v>
@@ -3134,7 +3586,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>848</v>
@@ -3217,7 +3669,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>830</v>
@@ -3300,7 +3752,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>608</v>
@@ -3383,7 +3835,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>1153</v>
@@ -3466,7 +3918,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>613</v>
@@ -3549,7 +4001,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="C30">
         <v>710</v>
@@ -3632,7 +4084,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>934</v>
@@ -3715,7 +4167,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>594</v>
@@ -3798,7 +4250,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>895</v>
@@ -3881,7 +4333,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>916</v>
@@ -3964,7 +4416,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>668</v>
@@ -4047,7 +4499,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>923</v>
@@ -4130,7 +4582,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>1170</v>
@@ -4213,7 +4665,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>1198</v>
@@ -4296,7 +4748,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>1090</v>
@@ -4379,7 +4831,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>1077</v>
@@ -4462,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>802</v>
@@ -4545,7 +4997,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>792</v>
@@ -4628,7 +5080,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>1142</v>
@@ -4711,7 +5163,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>1105</v>
@@ -4794,7 +5246,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>638</v>
@@ -4877,7 +5329,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>656</v>
@@ -4960,7 +5412,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>1184</v>
@@ -5043,7 +5495,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>850</v>
@@ -5126,7 +5578,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>623</v>
@@ -5209,7 +5661,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>745</v>
@@ -5292,7 +5744,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>1111</v>
@@ -5375,7 +5827,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>1086</v>
@@ -5458,7 +5910,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>832</v>
@@ -5541,7 +5993,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>644</v>
@@ -5624,7 +6076,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <v>846</v>
@@ -5707,7 +6159,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C56">
         <v>428</v>
@@ -5790,7 +6242,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C57">
         <v>1127</v>
@@ -5873,7 +6325,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C58">
         <v>1087</v>
@@ -5956,7 +6408,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C59">
         <v>970</v>
@@ -6039,7 +6491,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C60">
         <v>1112</v>
@@ -6122,7 +6574,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C61">
         <v>661</v>
@@ -6205,7 +6657,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C62">
         <v>901</v>
@@ -6288,7 +6740,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C63">
         <v>918</v>
@@ -6371,7 +6823,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C64">
         <v>674</v>
@@ -6454,7 +6906,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="C65">
         <v>1247</v>
@@ -6537,7 +6989,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C66">
         <v>1130</v>
@@ -6620,7 +7072,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C67">
         <v>1090</v>
@@ -6703,7 +7155,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C68">
         <v>1134</v>
@@ -6786,7 +7238,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C69">
         <v>630</v>
@@ -6869,7 +7321,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C70">
         <v>630</v>
@@ -6952,7 +7404,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C71">
         <v>1084</v>
@@ -7035,7 +7487,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C72">
         <v>1106</v>
@@ -7118,7 +7570,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C73">
         <v>1081</v>
@@ -7201,7 +7653,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C74">
         <v>1158</v>
@@ -7284,7 +7736,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C75">
         <v>908</v>
@@ -7367,7 +7819,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C76">
         <v>765</v>
@@ -7450,7 +7902,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C77">
         <v>596</v>
@@ -7533,7 +7985,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C78">
         <v>721</v>
@@ -7616,7 +8068,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C79">
         <v>775</v>
@@ -7699,7 +8151,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C80">
         <v>794</v>
@@ -7782,7 +8234,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C81">
         <v>662</v>
@@ -7865,7 +8317,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="C82">
         <v>629</v>
@@ -7948,7 +8400,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C83">
         <v>1138</v>
@@ -8031,7 +8483,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C84">
         <v>1053</v>
@@ -8114,7 +8566,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="C85">
         <v>1139</v>
@@ -8197,7 +8649,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="C86">
         <v>1204</v>
@@ -8280,7 +8732,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C87">
         <v>843</v>
@@ -8363,7 +8815,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C88">
         <v>957</v>
@@ -8446,7 +8898,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C89">
         <v>791</v>
@@ -8529,7 +8981,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C90">
         <v>1005</v>
@@ -8612,7 +9064,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C91">
         <v>913</v>
@@ -8695,7 +9147,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C92">
         <v>1007</v>
@@ -8778,7 +9230,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C93">
         <v>1059</v>
@@ -8861,7 +9313,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C94">
         <v>888</v>
@@ -8944,7 +9396,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C95">
         <v>685</v>
@@ -9027,7 +9479,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="C96">
         <v>325</v>
@@ -9110,7 +9562,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C97">
         <v>940</v>
@@ -9193,7 +9645,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="C98">
         <v>757</v>
@@ -9276,7 +9728,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="C99">
         <v>844</v>
@@ -9359,7 +9811,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="C100">
         <v>956</v>
@@ -9442,7 +9894,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C101">
         <v>958</v>
@@ -9525,7 +9977,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="C102">
         <v>1003</v>
@@ -9608,7 +10060,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C103">
         <v>1018</v>
@@ -9691,7 +10143,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C104">
         <v>811</v>
@@ -9774,7 +10226,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C105">
         <v>969</v>
@@ -9857,7 +10309,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C106">
         <v>749</v>
@@ -9940,7 +10392,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C107">
         <v>1102</v>
@@ -10023,7 +10475,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="C108">
         <v>759</v>
@@ -10106,7 +10558,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C109">
         <v>636</v>
@@ -10189,7 +10641,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C110">
         <v>928</v>
@@ -10272,7 +10724,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C111">
         <v>1111</v>
@@ -10355,7 +10807,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C112">
         <v>959</v>
@@ -10438,7 +10890,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C113">
         <v>1115</v>
@@ -10521,7 +10973,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C114">
         <v>1174</v>
@@ -10604,7 +11056,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C115">
         <v>1025</v>
@@ -10687,7 +11139,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C116">
         <v>1149</v>
@@ -10770,7 +11222,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C117">
         <v>1176</v>
@@ -10853,7 +11305,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C118">
         <v>857</v>
@@ -10936,7 +11388,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="C119">
         <v>818</v>
@@ -11019,7 +11471,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="C120">
         <v>684</v>
@@ -11102,7 +11554,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C121">
         <v>981</v>
@@ -11185,7 +11637,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C122">
         <v>768</v>
@@ -11268,7 +11720,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="C123">
         <v>1199</v>
@@ -11351,7 +11803,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="C124">
         <v>1161</v>
@@ -11434,7 +11886,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C125">
         <v>1149</v>
@@ -11517,7 +11969,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="C126">
         <v>1094</v>
@@ -11600,7 +12052,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C127">
         <v>884</v>
@@ -11683,7 +12135,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C128">
         <v>1179</v>
@@ -11766,7 +12218,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C129">
         <v>1119</v>
@@ -11849,7 +12301,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C130">
         <v>1057</v>
@@ -11932,7 +12384,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C131">
         <v>884</v>
@@ -12015,7 +12467,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C132">
         <v>1052</v>
@@ -12098,7 +12550,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C133">
         <v>1020</v>
@@ -12181,7 +12633,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C134">
         <v>1059</v>
@@ -12264,7 +12716,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C135">
         <v>821</v>
@@ -12347,7 +12799,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C136">
         <v>734</v>
@@ -12430,7 +12882,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C137">
         <v>1041</v>
@@ -12513,7 +12965,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C138">
         <v>790</v>
@@ -12596,7 +13048,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C139">
         <v>1174</v>
@@ -12679,7 +13131,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="C140">
         <v>1234</v>
@@ -12762,7 +13214,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C141">
         <v>1015</v>
@@ -12845,7 +13297,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="C142">
         <v>1064</v>
@@ -12928,7 +13380,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="C143">
         <v>741</v>
@@ -13011,7 +13463,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>4</v>
+        <v>133</v>
       </c>
       <c r="C144">
         <v>710</v>
@@ -13094,7 +13546,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C145">
         <v>1127</v>
@@ -13177,7 +13629,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C146">
         <v>1127</v>
@@ -13260,7 +13712,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C147">
         <v>1129</v>
@@ -13343,7 +13795,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C148">
         <v>1038</v>
@@ -13426,7 +13878,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C149">
         <v>981</v>
@@ -13509,7 +13961,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C150">
         <v>1236</v>
@@ -13592,7 +14044,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C151">
         <v>1228</v>
@@ -13675,7 +14127,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C152">
         <v>1179</v>
@@ -13758,7 +14210,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C153">
         <v>612</v>
@@ -13841,7 +14293,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="C154">
         <v>1031</v>
@@ -13924,7 +14376,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C155">
         <v>1132</v>
@@ -14007,7 +14459,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C156">
         <v>782</v>
@@ -14090,7 +14542,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C157">
         <v>675</v>
@@ -14173,7 +14625,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C158">
         <v>936</v>
@@ -14256,7 +14708,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C159">
         <v>1187</v>
@@ -14339,7 +14791,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C160">
         <v>925</v>
@@ -14422,7 +14874,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C161">
         <v>1204</v>
@@ -14505,7 +14957,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="C162">
         <v>1136</v>
@@ -14588,7 +15040,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C163">
         <v>902</v>
@@ -14671,7 +15123,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C164">
         <v>1123</v>
@@ -14754,7 +15206,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C165">
         <v>1173</v>
@@ -14837,7 +15289,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C166">
         <v>1187</v>
@@ -14920,7 +15372,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C167">
         <v>1162</v>
@@ -15003,7 +15455,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C168">
         <v>787</v>
@@ -15086,7 +15538,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C169">
         <v>705</v>
@@ -15169,7 +15621,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="C170">
         <v>761</v>
@@ -15252,7 +15704,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="C171">
         <v>674</v>
@@ -15335,7 +15787,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C172">
         <v>770</v>
@@ -15418,7 +15870,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C173">
         <v>742</v>
@@ -15501,7 +15953,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C174">
         <v>1099</v>
@@ -15584,7 +16036,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C175">
         <v>825</v>
@@ -15667,7 +16119,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C176">
         <v>837</v>
@@ -15750,7 +16202,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C177">
         <v>892</v>
@@ -15833,7 +16285,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="C178">
         <v>950</v>
@@ -15916,7 +16368,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="C179">
         <v>831</v>
@@ -15999,7 +16451,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="C180">
         <v>746</v>
@@ -16082,7 +16534,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C181">
         <v>1179</v>
@@ -16165,7 +16617,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C182">
         <v>1034</v>
@@ -16248,7 +16700,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C183">
         <v>1112</v>
@@ -16331,7 +16783,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C184">
         <v>744</v>
@@ -16414,7 +16866,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C185">
         <v>1134</v>
@@ -16497,7 +16949,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="C186">
         <v>1074</v>
@@ -16580,7 +17032,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C187">
         <v>795</v>
@@ -16663,7 +17115,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C188">
         <v>980</v>
@@ -16746,7 +17198,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C189">
         <v>1043</v>
@@ -16829,7 +17281,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C190">
         <v>1204</v>
@@ -16912,7 +17364,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="C191">
         <v>1142</v>
@@ -16995,7 +17447,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C192">
         <v>963</v>
@@ -17078,7 +17530,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="C193">
         <v>1116</v>
@@ -17161,7 +17613,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="C194">
         <v>1023</v>
@@ -17244,7 +17696,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="C195">
         <v>969</v>
@@ -17327,7 +17779,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="C196">
         <v>860</v>
@@ -17410,7 +17862,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="C197">
         <v>723</v>
@@ -17493,7 +17945,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="C198">
         <v>697</v>
@@ -17576,7 +18028,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C199">
         <v>873</v>
@@ -17659,7 +18111,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C200">
         <v>832</v>
@@ -17742,7 +18194,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="C201">
         <v>801</v>
@@ -17825,7 +18277,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="C202">
         <v>883</v>
@@ -17908,7 +18360,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="C203">
         <v>460</v>
@@ -17991,7 +18443,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C204">
         <v>1179</v>
@@ -18074,7 +18526,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C205">
         <v>958</v>
@@ -18157,7 +18609,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="C206">
         <v>1006</v>
@@ -18240,7 +18692,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C207">
         <v>1060</v>
@@ -18323,7 +18775,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C208">
         <v>630</v>
@@ -18406,7 +18858,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C209">
         <v>885</v>
@@ -18489,7 +18941,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>30</v>
+        <v>191</v>
       </c>
       <c r="C210">
         <v>1025</v>
@@ -18572,7 +19024,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="C211">
         <v>922</v>
@@ -18655,7 +19107,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="C212">
         <v>1099</v>
@@ -18738,7 +19190,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="C213">
         <v>637</v>
@@ -18821,7 +19273,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="C214">
         <v>658</v>
@@ -18904,7 +19356,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>5</v>
+        <v>195</v>
       </c>
       <c r="C215">
         <v>855</v>
@@ -18987,7 +19439,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="C216">
         <v>1083</v>
@@ -19070,7 +19522,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="C217">
         <v>1089</v>
@@ -19153,7 +19605,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="C218">
         <v>660</v>
@@ -19236,7 +19688,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C219">
         <v>670</v>
@@ -19319,7 +19771,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="C220">
         <v>610</v>
@@ -19402,7 +19854,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C221">
         <v>604</v>
@@ -19485,7 +19937,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="C222">
         <v>1126</v>
@@ -19568,7 +20020,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="C223">
         <v>872</v>
@@ -19651,7 +20103,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="C224">
         <v>957</v>
@@ -19734,7 +20186,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="C225">
         <v>970</v>
@@ -19817,7 +20269,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="C226">
         <v>702</v>
@@ -19900,7 +20352,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="C227">
         <v>564</v>
@@ -19983,7 +20435,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="C228">
         <v>501</v>
@@ -20066,7 +20518,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>3</v>
+        <v>209</v>
       </c>
       <c r="C229">
         <v>803</v>
@@ -20149,7 +20601,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>4</v>
+        <v>210</v>
       </c>
       <c r="C230">
         <v>818</v>
@@ -20232,7 +20684,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="C231">
         <v>942</v>
@@ -20315,7 +20767,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="C232">
         <v>1039</v>
@@ -20398,7 +20850,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="C233">
         <v>795</v>
@@ -20481,7 +20933,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="C234">
         <v>774</v>
@@ -20564,7 +21016,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="C235">
         <v>1116</v>
@@ -20647,7 +21099,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="C236">
         <v>1005</v>
@@ -20730,7 +21182,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="C237">
         <v>560</v>
@@ -20813,7 +21265,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="C238">
         <v>1188</v>
@@ -20896,7 +21348,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="C239">
         <v>1145</v>
@@ -20979,7 +21431,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="C240">
         <v>1068</v>
@@ -21062,7 +21514,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
       <c r="C241">
         <v>833</v>
@@ -21145,7 +21597,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>30</v>
+        <v>222</v>
       </c>
       <c r="C242">
         <v>684</v>
@@ -21228,7 +21680,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>31</v>
+        <v>223</v>
       </c>
       <c r="C243">
         <v>633</v>
@@ -21311,7 +21763,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="C244">
         <v>1033</v>
@@ -21394,7 +21846,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="C245">
         <v>1031</v>
@@ -21477,7 +21929,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>91</v>
+        <v>226</v>
       </c>
       <c r="C246">
         <v>670</v>
@@ -21560,7 +22012,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>6</v>
+        <v>227</v>
       </c>
       <c r="C247">
         <v>771</v>
@@ -21643,7 +22095,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>11</v>
+        <v>228</v>
       </c>
       <c r="C248">
         <v>1105</v>
@@ -21726,7 +22178,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="C249">
         <v>1061</v>
@@ -21809,7 +22261,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="C250">
         <v>1037</v>
@@ -21892,7 +22344,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="C251">
         <v>753</v>
@@ -21975,7 +22427,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="C252">
         <v>1097</v>
@@ -22058,7 +22510,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="C253">
         <v>1146</v>
@@ -22141,7 +22593,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="C254">
         <v>828</v>
@@ -22224,7 +22676,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="C255">
         <v>625</v>
@@ -22307,7 +22759,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="C256">
         <v>991</v>
@@ -22390,7 +22842,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>164</v>
+        <v>236</v>
       </c>
       <c r="C257">
         <v>1168</v>
@@ -22473,7 +22925,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="C258">
         <v>916</v>
@@ -22556,7 +23008,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="C259">
         <v>1047</v>
@@ -22639,7 +23091,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="C260">
         <v>668</v>
@@ -22722,7 +23174,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="C261">
         <v>1150</v>
@@ -22805,7 +23257,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C262">
         <v>1160</v>
@@ -22888,7 +23340,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C263">
         <v>1187</v>
@@ -22971,7 +23423,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="C264">
         <v>620</v>
@@ -23054,7 +23506,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>5</v>
+        <v>242</v>
       </c>
       <c r="C265">
         <v>534</v>
@@ -23137,7 +23589,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>166</v>
+        <v>243</v>
       </c>
       <c r="C266">
         <v>502</v>
@@ -23220,7 +23672,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>6</v>
+        <v>244</v>
       </c>
       <c r="C267">
         <v>1013</v>
@@ -23303,7 +23755,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>6</v>
+        <v>245</v>
       </c>
       <c r="C268">
         <v>504</v>
@@ -23386,7 +23838,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>6</v>
+        <v>246</v>
       </c>
       <c r="C269">
         <v>998</v>
@@ -23469,7 +23921,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>30</v>
+        <v>247</v>
       </c>
       <c r="C270">
         <v>1174</v>
@@ -23552,7 +24004,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>31</v>
+        <v>248</v>
       </c>
       <c r="C271">
         <v>1105</v>
@@ -23635,7 +24087,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>31</v>
+        <v>249</v>
       </c>
       <c r="C272">
         <v>1045</v>
@@ -23718,7 +24170,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="C273">
         <v>901</v>
@@ -23801,7 +24253,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="C274">
         <v>1088</v>
@@ -23884,7 +24336,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>188</v>
+        <v>252</v>
       </c>
       <c r="C275">
         <v>1046</v>
@@ -23967,7 +24419,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>189</v>
+        <v>253</v>
       </c>
       <c r="C276">
         <v>1136</v>
@@ -24050,7 +24502,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>189</v>
+        <v>254</v>
       </c>
       <c r="C277">
         <v>1086</v>
@@ -24133,7 +24585,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="C278">
         <v>734</v>
@@ -24216,7 +24668,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="C279">
         <v>891</v>
@@ -24299,7 +24751,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="C280">
         <v>1117</v>
@@ -24382,7 +24834,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="C281">
         <v>1018</v>
@@ -24465,7 +24917,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>194</v>
+        <v>258</v>
       </c>
       <c r="C282">
         <v>1172</v>
@@ -24548,7 +25000,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="C283">
         <v>1164</v>
@@ -24631,7 +25083,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="C284">
         <v>615</v>
@@ -24714,7 +25166,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>196</v>
+        <v>260</v>
       </c>
       <c r="C285">
         <v>637</v>
@@ -24797,7 +25249,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="C286">
         <v>1013</v>
@@ -24880,7 +25332,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>17</v>
+        <v>262</v>
       </c>
       <c r="C287">
         <v>1086</v>
@@ -24963,7 +25415,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="C288">
         <v>1136</v>
@@ -25046,7 +25498,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>18</v>
+        <v>264</v>
       </c>
       <c r="C289">
         <v>1144</v>
@@ -25129,7 +25581,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="C290">
         <v>964</v>
@@ -25212,7 +25664,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C291">
         <v>871</v>
@@ -25295,7 +25747,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="C292">
         <v>850</v>
@@ -25378,7 +25830,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="C293">
         <v>983</v>
@@ -25461,7 +25913,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="C294">
         <v>1004</v>
@@ -25544,7 +25996,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="C295">
         <v>695</v>
@@ -25627,7 +26079,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>201</v>
+        <v>271</v>
       </c>
       <c r="C296">
         <v>687</v>
@@ -25710,7 +26162,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="C297">
         <v>1106</v>
@@ -25793,7 +26245,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="C298">
         <v>781</v>
@@ -25876,7 +26328,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
       <c r="C299">
         <v>954</v>
@@ -25959,7 +26411,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="C300">
         <v>1004</v>
@@ -26042,7 +26494,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="C301">
         <v>733</v>
@@ -26125,7 +26577,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="C302">
         <v>707</v>
@@ -26208,7 +26660,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>182</v>
+        <v>277</v>
       </c>
       <c r="C303">
         <v>838</v>
@@ -26291,7 +26743,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>183</v>
+        <v>278</v>
       </c>
       <c r="C304">
         <v>1132</v>
@@ -26374,7 +26826,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="C305">
         <v>1132</v>
@@ -26457,7 +26909,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="C306">
         <v>952</v>
@@ -26540,7 +26992,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>208</v>
+        <v>281</v>
       </c>
       <c r="C307">
         <v>885</v>
@@ -26623,7 +27075,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="C308">
         <v>1125</v>
@@ -26706,7 +27158,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>63</v>
+        <v>283</v>
       </c>
       <c r="C309">
         <v>839</v>
@@ -26789,7 +27241,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>63</v>
+        <v>284</v>
       </c>
       <c r="C310">
         <v>826</v>
@@ -26872,7 +27324,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>63</v>
+        <v>285</v>
       </c>
       <c r="C311">
         <v>783</v>
@@ -26955,7 +27407,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>63</v>
+        <v>286</v>
       </c>
       <c r="C312">
         <v>1025</v>
@@ -27038,7 +27490,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="C313">
         <v>620</v>
@@ -27121,7 +27573,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="C314">
         <v>928</v>
@@ -27204,7 +27656,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="C315">
         <v>667</v>
@@ -27287,7 +27739,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>212</v>
+        <v>290</v>
       </c>
       <c r="C316">
         <v>1030</v>
@@ -27370,7 +27822,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>213</v>
+        <v>291</v>
       </c>
       <c r="C317">
         <v>986</v>
@@ -27453,7 +27905,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>214</v>
+        <v>292</v>
       </c>
       <c r="C318">
         <v>788</v>
@@ -27536,7 +27988,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>215</v>
+        <v>293</v>
       </c>
       <c r="C319">
         <v>830</v>
@@ -27619,7 +28071,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>216</v>
+        <v>294</v>
       </c>
       <c r="C320">
         <v>902</v>
@@ -27702,7 +28154,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>217</v>
+        <v>295</v>
       </c>
       <c r="C321">
         <v>987</v>
@@ -27785,7 +28237,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="C322">
         <v>579</v>
@@ -27868,7 +28320,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>219</v>
+        <v>297</v>
       </c>
       <c r="C323">
         <v>811</v>
@@ -27951,7 +28403,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="C324">
         <v>769</v>
@@ -28034,7 +28486,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="C325">
         <v>1121</v>
@@ -28117,7 +28569,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="C326">
         <v>578</v>
@@ -28200,7 +28652,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="C327">
         <v>722</v>
@@ -28283,7 +28735,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="C328">
         <v>808</v>
@@ -28366,7 +28818,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="C329">
         <v>1048</v>
@@ -28449,7 +28901,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>160</v>
+        <v>303</v>
       </c>
       <c r="C330">
         <v>1102</v>
@@ -28532,7 +28984,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>155</v>
+        <v>304</v>
       </c>
       <c r="C331">
         <v>1065</v>
@@ -28615,7 +29067,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>155</v>
+        <v>305</v>
       </c>
       <c r="C332">
         <v>1110</v>
@@ -28698,7 +29150,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>155</v>
+        <v>306</v>
       </c>
       <c r="C333">
         <v>819</v>
@@ -28781,7 +29233,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>224</v>
+        <v>307</v>
       </c>
       <c r="C334">
         <v>1012</v>
@@ -28864,7 +29316,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>225</v>
+        <v>308</v>
       </c>
       <c r="C335">
         <v>1016</v>
@@ -28947,7 +29399,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>225</v>
+        <v>309</v>
       </c>
       <c r="C336">
         <v>859</v>
@@ -29030,7 +29482,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>226</v>
+        <v>310</v>
       </c>
       <c r="C337">
         <v>1069</v>
@@ -29113,7 +29565,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="C338">
         <v>895</v>
@@ -29196,7 +29648,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>228</v>
+        <v>311</v>
       </c>
       <c r="C339">
         <v>703</v>
@@ -29279,7 +29731,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="C340">
         <v>986</v>
@@ -29362,7 +29814,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>91</v>
+        <v>313</v>
       </c>
       <c r="C341">
         <v>867</v>
@@ -29445,7 +29897,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>6</v>
+        <v>314</v>
       </c>
       <c r="C342">
         <v>886</v>
@@ -29528,7 +29980,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>6</v>
+        <v>314</v>
       </c>
       <c r="C343">
         <v>890</v>
@@ -29611,7 +30063,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>230</v>
+        <v>315</v>
       </c>
       <c r="C344">
         <v>1120</v>
@@ -29694,7 +30146,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>231</v>
+        <v>316</v>
       </c>
       <c r="C345">
         <v>1067</v>
@@ -29777,7 +30229,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>231</v>
+        <v>317</v>
       </c>
       <c r="C346">
         <v>1157</v>
@@ -29860,7 +30312,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>232</v>
+        <v>318</v>
       </c>
       <c r="C347">
         <v>769</v>
@@ -29943,7 +30395,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="C348">
         <v>766</v>
@@ -30026,7 +30478,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>233</v>
+        <v>320</v>
       </c>
       <c r="C349">
         <v>1141</v>
@@ -30109,7 +30561,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>234</v>
+        <v>321</v>
       </c>
       <c r="C350">
         <v>933</v>
@@ -30192,7 +30644,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>234</v>
+        <v>321</v>
       </c>
       <c r="C351">
         <v>959</v>
@@ -30275,7 +30727,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="C352">
         <v>727</v>
@@ -30358,7 +30810,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>236</v>
+        <v>323</v>
       </c>
       <c r="C353">
         <v>1197</v>
@@ -30441,7 +30893,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>162</v>
+        <v>324</v>
       </c>
       <c r="C354">
         <v>747</v>
@@ -30524,7 +30976,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>8</v>
+        <v>325</v>
       </c>
       <c r="C355">
         <v>567</v>
@@ -30607,7 +31059,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>8</v>
+        <v>326</v>
       </c>
       <c r="C356">
         <v>1021</v>
@@ -30690,7 +31142,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>195</v>
+        <v>327</v>
       </c>
       <c r="C357">
         <v>1044</v>
@@ -30773,7 +31225,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>196</v>
+        <v>328</v>
       </c>
       <c r="C358">
         <v>825</v>
@@ -30856,7 +31308,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="C359">
         <v>818</v>
@@ -30939,7 +31391,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>238</v>
+        <v>330</v>
       </c>
       <c r="C360">
         <v>902</v>
@@ -31022,7 +31474,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>239</v>
+        <v>331</v>
       </c>
       <c r="C361">
         <v>996</v>
@@ -31105,7 +31557,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>240</v>
+        <v>332</v>
       </c>
       <c r="C362">
         <v>1024</v>
@@ -31188,7 +31640,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>91</v>
+        <v>333</v>
       </c>
       <c r="C363">
         <v>1069</v>
@@ -31271,7 +31723,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>6</v>
+        <v>334</v>
       </c>
       <c r="C364">
         <v>1124</v>
@@ -31354,7 +31806,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>78</v>
+        <v>335</v>
       </c>
       <c r="C365">
         <v>1091</v>
@@ -31437,7 +31889,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="C366">
         <v>1002</v>
@@ -31520,7 +31972,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="C367">
         <v>828</v>
@@ -31603,7 +32055,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>241</v>
+        <v>338</v>
       </c>
       <c r="C368">
         <v>1020</v>
@@ -31686,7 +32138,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>241</v>
+        <v>339</v>
       </c>
       <c r="C369">
         <v>1173</v>
@@ -31769,7 +32221,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>30</v>
+        <v>340</v>
       </c>
       <c r="C370">
         <v>839</v>
@@ -31852,7 +32304,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>31</v>
+        <v>341</v>
       </c>
       <c r="C371">
         <v>762</v>
@@ -31935,7 +32387,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>242</v>
+        <v>342</v>
       </c>
       <c r="C372">
         <v>1160</v>
@@ -32018,7 +32470,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>243</v>
+        <v>343</v>
       </c>
       <c r="C373">
         <v>709</v>
@@ -32101,7 +32553,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>244</v>
+        <v>344</v>
       </c>
       <c r="C374">
         <v>779</v>
@@ -32184,7 +32636,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>245</v>
+        <v>345</v>
       </c>
       <c r="C375">
         <v>1171</v>
@@ -32267,7 +32719,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>246</v>
+        <v>346</v>
       </c>
       <c r="C376">
         <v>633</v>
@@ -32350,7 +32802,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>247</v>
+        <v>347</v>
       </c>
       <c r="C377">
         <v>580</v>
@@ -32433,7 +32885,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>248</v>
+        <v>348</v>
       </c>
       <c r="C378">
         <v>946</v>
@@ -32516,7 +32968,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>208</v>
+        <v>349</v>
       </c>
       <c r="C379">
         <v>620</v>
@@ -32599,7 +33051,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>249</v>
+        <v>350</v>
       </c>
       <c r="C380">
         <v>807</v>
@@ -32682,7 +33134,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>250</v>
+        <v>351</v>
       </c>
       <c r="C381">
         <v>560</v>
@@ -32765,7 +33217,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>251</v>
+        <v>352</v>
       </c>
       <c r="C382">
         <v>1158</v>
@@ -32848,7 +33300,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>252</v>
+        <v>353</v>
       </c>
       <c r="C383">
         <v>1161</v>
@@ -32931,7 +33383,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>31</v>
+        <v>354</v>
       </c>
       <c r="C384">
         <v>700</v>
@@ -33014,7 +33466,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>31</v>
+        <v>355</v>
       </c>
       <c r="C385">
         <v>744</v>
@@ -33097,7 +33549,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>253</v>
+        <v>356</v>
       </c>
       <c r="C386">
         <v>1010</v>
@@ -33180,7 +33632,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>254</v>
+        <v>357</v>
       </c>
       <c r="C387">
         <v>1044</v>
@@ -33263,7 +33715,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="C388">
         <v>527</v>
@@ -33346,7 +33798,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>256</v>
+        <v>359</v>
       </c>
       <c r="C389">
         <v>853</v>
@@ -33429,7 +33881,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>257</v>
+        <v>360</v>
       </c>
       <c r="C390">
         <v>1024</v>
@@ -33512,7 +33964,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>258</v>
+        <v>361</v>
       </c>
       <c r="C391">
         <v>1023</v>
@@ -33595,7 +34047,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>182</v>
+        <v>362</v>
       </c>
       <c r="C392">
         <v>978</v>
@@ -33678,7 +34130,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>183</v>
+        <v>363</v>
       </c>
       <c r="C393">
         <v>899</v>
@@ -33761,7 +34213,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>30</v>
+        <v>364</v>
       </c>
       <c r="C394">
         <v>1120</v>
@@ -33844,7 +34296,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>31</v>
+        <v>365</v>
       </c>
       <c r="C395">
         <v>1044</v>
@@ -33927,7 +34379,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="C396">
         <v>962</v>
@@ -34010,7 +34462,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="C397">
         <v>878</v>
@@ -34093,7 +34545,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>40</v>
+        <v>368</v>
       </c>
       <c r="C398">
         <v>940</v>
@@ -34176,7 +34628,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>41</v>
+        <v>369</v>
       </c>
       <c r="C399">
         <v>1119</v>
@@ -34259,7 +34711,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>42</v>
+        <v>370</v>
       </c>
       <c r="C400">
         <v>737</v>
@@ -34342,7 +34794,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>43</v>
+        <v>371</v>
       </c>
       <c r="C401">
         <v>639</v>
@@ -34425,7 +34877,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>44</v>
+        <v>372</v>
       </c>
       <c r="C402">
         <v>749</v>
@@ -34508,7 +34960,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>45</v>
+        <v>373</v>
       </c>
       <c r="C403">
         <v>706</v>
@@ -34591,7 +35043,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>46</v>
+        <v>374</v>
       </c>
       <c r="C404">
         <v>1079</v>
@@ -34674,7 +35126,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>259</v>
+        <v>375</v>
       </c>
       <c r="C405">
         <v>1113</v>
@@ -34757,7 +35209,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>260</v>
+        <v>376</v>
       </c>
       <c r="C406">
         <v>1029</v>
@@ -34840,7 +35292,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>261</v>
+        <v>377</v>
       </c>
       <c r="C407">
         <v>578</v>
@@ -34923,7 +35375,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>262</v>
+        <v>378</v>
       </c>
       <c r="C408">
         <v>909</v>
@@ -35006,7 +35458,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>263</v>
+        <v>379</v>
       </c>
       <c r="C409">
         <v>644</v>
